--- a/workbooks/05 Shortcuts 3 - Format.xlsx
+++ b/workbooks/05 Shortcuts 3 - Format.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="608">
   <si>
     <t>Challenge</t>
   </si>
@@ -2103,6 +2103,12 @@
   </si>
   <si>
     <t>Boss F8</t>
+  </si>
+  <si>
+    <t>The key above Caps Lock.</t>
+  </si>
+  <si>
+    <t>TAB</t>
   </si>
   <si>
     <t>F8</t>
@@ -3100,7 +3106,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3110,12 +3116,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3125,32 +3131,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3160,30 +3166,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('S3-1 Number Skins'!$G$16:$G$50)&amp;" / 280"</f>
@@ -3198,15 +3204,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('S3-2 Text Style'!$G$14:$G$39)&amp;" / 190"</f>
@@ -3221,15 +3227,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('S3-3 Format Power'!$G$17:$G$51)&amp;" / 280"</f>
@@ -3244,15 +3250,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3267,12 +3273,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B18" s="12" cm="1" t="str">
         <f t="array" ref="B18">(SUM('S3-1 Number Skins'!$G$16:$G$50)+SUM('S3-2 Text Style'!$G$14:$G$39)+SUM('S3-3 Format Power'!$G$17:$G$51)+SUM(Boss!$G$14:$G$33))&amp;" / 910"</f>
@@ -3281,19 +3287,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('S3-1 Number Skins'!$G$16:$G$50)+SUM('S3-2 Text Style'!$G$14:$G$39)+SUM('S3-3 Format Power'!$G$17:$G$51)+SUM(Boss!$G$14:$G$33))/910,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=8),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 8)","—")</f>
@@ -3302,7 +3308,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -3311,7 +3317,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>
@@ -3344,7 +3350,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3352,259 +3358,259 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>227</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>127</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.75" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>122</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>137</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>278</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>128</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>317</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>121</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>138</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>90</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -5248,24 +5254,15 @@
         <v>501</v>
       </c>
       <c r="B84" t="s">
-        <v>120</v>
+        <v>502</v>
       </c>
       <c r="E84" t="s">
-        <v>152</v>
-      </c>
-      <c r="F84" t="s">
-        <v>153</v>
-      </c>
-      <c r="G84" t="s">
-        <v>154</v>
-      </c>
-      <c r="H84" t="s">
-        <v>155</v>
+        <v>503</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B85" t="s">
         <v>188</v>
@@ -5273,7 +5270,7 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B86" t="s">
         <v>193</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B87" t="s">
         <v>203</v>
@@ -5289,7 +5286,7 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s">
         <v>208</v>
@@ -5297,34 +5294,34 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B90" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B91" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B92" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -8494,7 +8491,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8505,7 +8502,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8770,17 +8767,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="35.5" customHeight="1">
+    <row r="21" spans="1:7" ht="51.25" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B21" s="31" cm="1" t="str">
-        <f t="array" ref="B21">IF($C$10="OPEN","Which keys apply the Currency format?  (from S3-1 Number Skins)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
+        <f t="array" ref="B21">IF($C$10="OPEN","While typing a function name, which key inserts the highlighted AutoComplete suggestion?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
-        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$84:$H$84),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
+        <f t="array" ref="D21">IF($C$10="OPEN",IFERROR(_xlfn.LET(_xlpm.a,Boss!$C$21,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$84:$E$84),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN"),"LOCKED")</f>
         <v>LOCKED</v>
       </c>
       <c r="E21" s="22"/>
@@ -8795,7 +8792,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8806,7 +8803,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8834,14 +8831,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B26" s="31" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In the Boss Arena make B6:B8 currency (Ctrl+Shift+$). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$B$6)="C2",CELL("format",'Boss Arena'!$B$6)="C2-"),OR(CELL("format",'Boss Arena'!$B$7)="C2",CELL("format",'Boss Arena'!$B$7)="C2-"),OR(CELL("format",'Boss Arena'!$B$8)="C2",CELL("format",'Boss Arena'!$B$8)="C2-")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8859,14 +8856,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B27" s="31" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","Make C6:C8 percent (Ctrl+Shift+%). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$C$6)="P0"),OR(CELL("format",'Boss Arena'!$C$7)="P0"),OR(CELL("format",'Boss Arena'!$C$8)="P0")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8884,14 +8881,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B28" s="31" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","Make D6:D8 dates (Ctrl+Shift+#). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$D$6)="D1",CELL("format",'Boss Arena'!$D$6)="D4"),OR(CELL("format",'Boss Arena'!$D$7)="D1",CELL("format",'Boss Arena'!$D$7)="D4"),OR(CELL("format",'Boss Arena'!$D$8)="D1",CELL("format",'Boss Arena'!$D$8)="D4")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8909,14 +8906,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B29" s="31" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","Make E6:E8 times (Ctrl+Shift+@). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$E$6)="D7",CELL("format",'Boss Arena'!$E$6)="D6",CELL("format",'Boss Arena'!$E$6)="D9",CELL("format",'Boss Arena'!$E$6)="D8"),OR(CELL("format",'Boss Arena'!$E$7)="D7",CELL("format",'Boss Arena'!$E$7)="D6",CELL("format",'Boss Arena'!$E$7)="D9",CELL("format",'Boss Arena'!$E$7)="D8"),OR(CELL("format",'Boss Arena'!$E$8)="D7",CELL("format",'Boss Arena'!$E$8)="D6",CELL("format",'Boss Arena'!$E$8)="D9",CELL("format",'Boss Arena'!$E$8)="D8")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8934,14 +8931,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B30" s="31" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","F6:F8 wear currency. Reset them to General (Ctrl+Shift+~). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$F$6)="G"),OR(CELL("format",'Boss Arena'!$F$7)="G"),OR(CELL("format",'Boss Arena'!$F$8)="G")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8959,14 +8956,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B31" s="31" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","Give G6:G8 exactly 1 decimal place through Ctrl+1. Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$G$6)="F1",CELL("format",'Boss Arena'!$G$6)=",1"),OR(CELL("format",'Boss Arena'!$G$7)="F1",CELL("format",'Boss Arena'!$G$7)=",1"),OR(CELL("format",'Boss Arena'!$G$8)="F1",CELL("format",'Boss Arena'!$G$8)=",1")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8984,14 +8981,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B32" s="31" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","Center H6:H8 with Alt, H, A, C. Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(IFERROR(AND(CELL("prefix",'Boss Arena'!$H$6)="^",CELL("prefix",'Boss Arena'!$H$7)="^",CELL("prefix",'Boss Arena'!$H$8)="^"),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -9009,14 +9006,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B33" s="31" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","Make I6 a percent with Ctrl+Shift+%, then use F4 on I7 and I8. Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$I$6)="P0"),OR(CELL("format",'Boss Arena'!$I$7)="P0"),OR(CELL("format",'Boss Arena'!$I$8)="P0")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>

--- a/workbooks/05 Shortcuts 3 - Format.xlsx
+++ b/workbooks/05 Shortcuts 3 - Format.xlsx
@@ -7147,7 +7147,7 @@
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="21" cm="1" t="str">
-        <f t="array" ref="D39">IF('S3-2 Text Style'!$C$39="Done","✔ CLEAR · self-check","")</f>
+        <f t="array" ref="D39">IFERROR(IF('S3-2 Text Style'!$C$39="Done","✔ CLEAR · self-check",""),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E39" s="22"/>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="21" cm="1" t="str">
-        <f t="array" ref="D51">IF('S3-3 Format Power'!$C$51="Done","✔ CLEAR · self-check","")</f>
+        <f t="array" ref="D51">IFERROR(IF('S3-3 Format Power'!$C$51="Done","✔ CLEAR · self-check",""),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E51" s="22"/>

--- a/workbooks/05 Shortcuts 3 - Format.xlsx
+++ b/workbooks/05 Shortcuts 3 - Format.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="613">
   <si>
     <t>Challenge</t>
   </si>
@@ -1152,7 +1152,22 @@
     <t>A test that is always true.</t>
   </si>
   <si>
+    <t>=TRUE</t>
+  </si>
+  <si>
+    <t>=TRUE(</t>
+  </si>
+  <si>
+    <t>=TRUE()</t>
+  </si>
+  <si>
     <t>TRUE</t>
+  </si>
+  <si>
+    <t>TRUE(</t>
+  </si>
+  <si>
+    <t>TRUE()</t>
   </si>
   <si>
     <t>In IFS, what do you put as the last test to catch all remaining cases?  (from F2-4 Multi-Level)</t>
@@ -2306,7 +2321,7 @@
     <t>NEXT UP</t>
   </si>
   <si>
-    <t>Replay a stage: select its yellow answer cells and press Delete. Undo an arena drill with Ctrl+Z.</t>
+    <t>Replay a stage: select a run of its yellow cells (Ctrl+click to add more), then press Delete. Undo an arena drill with Ctrl+Z.</t>
   </si>
   <si>
     <t>CHEAT CODES ▸ FORMAT</t>
@@ -3106,7 +3121,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3116,12 +3131,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -3131,32 +3146,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -3166,30 +3181,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('S3-1 Number Skins'!$G$16:$G$50)&amp;" / 280"</f>
@@ -3204,15 +3219,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('S3-2 Text Style'!$G$14:$G$39)&amp;" / 190"</f>
@@ -3227,15 +3242,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('S3-3 Format Power'!$G$17:$G$51)&amp;" / 280"</f>
@@ -3250,15 +3265,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -3273,12 +3288,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B18" s="12" cm="1" t="str">
         <f t="array" ref="B18">(SUM('S3-1 Number Skins'!$G$16:$G$50)+SUM('S3-2 Text Style'!$G$14:$G$39)+SUM('S3-3 Format Power'!$G$17:$G$51)+SUM(Boss!$G$14:$G$33))&amp;" / 910"</f>
@@ -3287,19 +3302,19 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">_xlfn.LET(_xlpm.p,(SUM('S3-1 Number Skins'!$G$16:$G$50)+SUM('S3-2 Text Style'!$G$14:$G$39)+SUM('S3-3 Format Power'!$G$17:$G$51)+SUM(Boss!$G$14:$G$33))/910,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=8),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 8)","—")</f>
@@ -3308,16 +3323,16 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
-        <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
+        <f t="array" ref="B21">IFERROR(INDEX($A$13:$A$15,MATCH("☆☆☆",$D$13:$D$15,0))&amp;" "&amp;INDEX($B$13:$B$15,MATCH("☆☆☆",$D$13:$D$15,0)),IF(Start!$E$16="DEFEATED","All clear! Aim for rank S","the Boss"))</f>
         <v>S3-1 Number Skins</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -3350,7 +3365,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3358,259 +3373,259 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.75" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.5" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.5" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.5" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>227</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.75" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>229</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>127</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19.75" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>122</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>137</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>128</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>121</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>138</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>90</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -4300,39 +4315,54 @@
       <c r="E38" t="s">
         <v>259</v>
       </c>
+      <c r="F38" t="s">
+        <v>260</v>
+      </c>
+      <c r="G38" t="s">
+        <v>261</v>
+      </c>
+      <c r="H38" t="s">
+        <v>262</v>
+      </c>
+      <c r="I38" t="s">
+        <v>263</v>
+      </c>
+      <c r="J38" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B39" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E39" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F39" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G39" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H39" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I39" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J39" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C40" t="s">
         <v>227</v>
@@ -4352,10 +4382,10 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B41" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C41" t="s">
         <v>229</v>
@@ -4375,10 +4405,10 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C42" t="s">
         <v>127</v>
@@ -4387,7 +4417,7 @@
         <v>128</v>
       </c>
       <c r="F42" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G42" t="s">
         <v>229</v>
@@ -4398,10 +4428,10 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B43" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C43" t="s">
         <v>122</v>
@@ -4421,262 +4451,262 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B44" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E44" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F44" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B45" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E45" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F45" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B46" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E46" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F46" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B47" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E47" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B48" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E48" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E49" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F49" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E50" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F50" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E51" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F51" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E52" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E53" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F53" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="G53" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="H53" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="I53" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J53" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B54" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E54" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F54" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G54" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="H54" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="I54" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J54" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E55" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F55" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="G55" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="H55" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="I55" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="J55" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B56" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E56" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F56" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G56" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H56" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="I56" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J56" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E57" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F57" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="G57" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="H57" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E58" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B59" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C59" t="s">
         <v>137</v>
@@ -4696,19 +4726,19 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C60" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E60" t="s">
         <v>137</v>
       </c>
       <c r="F60" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G60" t="s">
         <v>122</v>
@@ -4719,10 +4749,10 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B61" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C61" t="s">
         <v>128</v>
@@ -4742,13 +4772,13 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B62" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C62" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E62" t="s">
         <v>227</v>
@@ -4760,21 +4790,21 @@
         <v>229</v>
       </c>
       <c r="H62" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B63" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C63" t="s">
         <v>121</v>
       </c>
       <c r="E63" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F63" t="s">
         <v>127</v>
@@ -4788,10 +4818,10 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C64" t="s">
         <v>138</v>
@@ -4811,16 +4841,16 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B65" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C65" t="s">
         <v>90</v>
       </c>
       <c r="E65" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F65" t="s">
         <v>127</v>
@@ -4834,190 +4864,190 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B66" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E66" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B67" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E67" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F67" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G67" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H67" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B68" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E68" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F68" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G68" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H68" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B69" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E69" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F69" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B70" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E70" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F70" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G70" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="H70" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="I70" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J70" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K70" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L70" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M70" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N70" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O70" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P70" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q70" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="R70" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="S70" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="T70" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E71" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F71" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="G71" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H71" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="I71" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J71" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K71" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="L71" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="M71" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="N71" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="O71" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="P71" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="Q71" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="R71" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="S71" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="T71" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B72" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E72" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="F72" t="s">
         <v>90</v>
@@ -5025,225 +5055,225 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B73" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B74" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E76" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B77" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E77" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B78" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E78" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F78" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G78" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H78" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B79" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E79" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F79" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="G79" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H79" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B80" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E80" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F80" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B81" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E81" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F81" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G81" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="H81" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="I81" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="J81" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K81" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L81" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M81" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="N81" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="O81" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="P81" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="Q81" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="R81" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="S81" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="T81" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B82" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E82" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F82" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="G82" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H82" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="I82" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J82" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K82" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="L82" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="M82" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="N82" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="O82" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="P82" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="Q82" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="R82" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="S82" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="T82" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B83" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E83" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="F83" t="s">
         <v>90</v>
@@ -5251,18 +5281,18 @@
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B84" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E84" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B85" t="s">
         <v>188</v>
@@ -5270,7 +5300,7 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B86" t="s">
         <v>193</v>
@@ -5278,7 +5308,7 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B87" t="s">
         <v>203</v>
@@ -5286,7 +5316,7 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B88" t="s">
         <v>208</v>
@@ -5294,34 +5324,34 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B89" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B90" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B91" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B92" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -6533,7 +6563,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6544,7 +6574,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -6850,11 +6880,11 @@
         <v>106</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
-        <f t="array" ref="D22">IFERROR(_xlfn.LET(_xlpm.a,'S3-2 Text Style'!$C$22,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$38:$E$38),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
+        <f t="array" ref="D22">IFERROR(_xlfn.LET(_xlpm.a,'S3-2 Text Style'!$C$22,IF(TRIM(_xlpm.a&amp;"")="","",IF(OR(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(UPPER(_xlpm.a)," ",""),"CONTROL","CTRL"),"CTL","CTRL"),"ESCAPE","ESC"),"RETURN","ENTER"),"PAGEDOWN","PGDN"),"PGDOWN","PGDN"),"PAGEUP","PGUP"),"ARROWKEYS","ARROW"),"ARROWKEY","ARROW"),"ARROWS","ARROW"),"DOWNARROW","DOWN"),"UPARROW","UP"),"LEFTARROW","LEFT"),"RIGHTARROW","RIGHT"),"ARROWDOWN","DOWN"),"ARROWUP","UP"),"ARROWLEFT","LEFT"),"ARROWRIGHT","RIGHT"),"↓","DOWN"),"↑","UP"),"←","LEFT"),"→","RIGHT"),"SPACEBAR","SPACE"),"−","-"),"MINUS","-"),"PLUS","+")=Key!$E$38:$J$38),"✔ CLEAR","✘ TRY AGAIN"))),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E22" s="22"/>
@@ -6872,7 +6902,7 @@
         <v>116</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -6928,7 +6958,7 @@
         <v>123</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="21" cm="1" t="str">
@@ -6950,7 +6980,7 @@
         <v>129</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="21" cm="1" t="str">
@@ -6972,7 +7002,7 @@
         <v>133</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="21" cm="1" t="str">
@@ -6994,7 +7024,7 @@
         <v>139</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -7024,7 +7054,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="B33" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7055,7 +7085,7 @@
         <v>156</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -7077,7 +7107,7 @@
         <v>162</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -7099,7 +7129,7 @@
         <v>168</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="21" cm="1" t="str">
@@ -7121,7 +7151,7 @@
         <v>174</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="21" cm="1" t="str">
@@ -7143,7 +7173,7 @@
         <v>180</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="21" cm="1" t="str">
@@ -7348,7 +7378,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7359,7 +7389,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -7411,7 +7441,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>137</v>
@@ -7422,10 +7452,10 @@
         <v>22</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35.5" customHeight="1">
@@ -7433,7 +7463,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>128</v>
@@ -7444,10 +7474,10 @@
         <v>28</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="67" customHeight="1">
@@ -7455,7 +7485,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>121</v>
@@ -7466,7 +7496,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>138</v>
@@ -7474,10 +7504,10 @@
     </row>
     <row r="13" spans="1:7" ht="51.25" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>90</v>
@@ -7522,7 +7552,7 @@
         <v>51</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="21" cm="1" t="str">
@@ -7544,7 +7574,7 @@
         <v>61</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="21" cm="1" t="str">
@@ -7566,7 +7596,7 @@
         <v>71</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="21" cm="1" t="str">
@@ -7588,7 +7618,7 @@
         <v>76</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="21" cm="1" t="str">
@@ -7610,7 +7640,7 @@
         <v>81</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" cm="1" t="str">
@@ -7632,7 +7662,7 @@
         <v>86</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="21" cm="1" t="str">
@@ -7654,7 +7684,7 @@
         <v>91</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="21" cm="1" t="str">
@@ -7676,7 +7706,7 @@
         <v>96</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="21" cm="1" t="str">
@@ -7698,7 +7728,7 @@
         <v>106</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="21" cm="1" t="str">
@@ -7720,7 +7750,7 @@
         <v>116</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="21" cm="1" t="str">
@@ -7776,7 +7806,7 @@
         <v>123</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="21" cm="1" t="str">
@@ -7798,7 +7828,7 @@
         <v>129</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="21" cm="1" t="str">
@@ -7820,7 +7850,7 @@
         <v>133</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="21" cm="1" t="str">
@@ -7842,7 +7872,7 @@
         <v>139</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="21" cm="1" t="str">
@@ -7864,7 +7894,7 @@
         <v>143</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="21" cm="1" t="str">
@@ -7886,7 +7916,7 @@
         <v>147</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C35" s="20"/>
       <c r="D35" s="21" cm="1" t="str">
@@ -7905,10 +7935,10 @@
     </row>
     <row r="36" spans="1:7" ht="19.75" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="21" cm="1" t="str">
@@ -7938,7 +7968,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="B39" s="11" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -7969,7 +7999,7 @@
         <v>156</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="21" cm="1" t="str">
@@ -7991,7 +8021,7 @@
         <v>162</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="21" cm="1" t="str">
@@ -8013,7 +8043,7 @@
         <v>168</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="21" cm="1" t="str">
@@ -8035,7 +8065,7 @@
         <v>174</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="21" cm="1" t="str">
@@ -8057,7 +8087,7 @@
         <v>180</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="21" cm="1" t="str">
@@ -8079,7 +8109,7 @@
         <v>186</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="21" cm="1" t="str">
@@ -8101,7 +8131,7 @@
         <v>189</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21" cm="1" t="str">
@@ -8123,10 +8153,10 @@
         <v>194</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D48" s="21" cm="1" t="str">
         <f t="array" ref="D48">IF(IFERROR(AND(OR(CELL("format",'S3-3 Arena'!$B$6)="F1",CELL("format",'S3-3 Arena'!$B$6)=",1"),OR(CELL("format",'S3-3 Arena'!$B$7)="F1",CELL("format",'S3-3 Arena'!$B$7)=",1"),OR(CELL("format",'S3-3 Arena'!$B$8)="F1",CELL("format",'S3-3 Arena'!$B$8)=",1"),OR(CELL("format",'S3-3 Arena'!$B$9)="F1",CELL("format",'S3-3 Arena'!$B$9)=",1")),FALSE),"✔ CLEAR","· not yet · press F9")</f>
@@ -8147,10 +8177,10 @@
         <v>199</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D49" s="21" cm="1" t="str">
         <f t="array" ref="D49">IF(IFERROR(AND(CELL("prefix",'S3-3 Arena'!$C$6)="^",CELL("prefix",'S3-3 Arena'!$C$7)="^",CELL("prefix",'S3-3 Arena'!$C$8)="^",CELL("prefix",'S3-3 Arena'!$C$9)="^"),FALSE),"✔ CLEAR","· not yet · press F9")</f>
@@ -8171,10 +8201,10 @@
         <v>204</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D50" s="21" cm="1" t="str">
         <f t="array" ref="D50">IF(IFERROR(AND(OR(CELL("format",'S3-3 Arena'!$D$6)="P0"),OR(CELL("format",'S3-3 Arena'!$D$7)="P0"),OR(CELL("format",'S3-3 Arena'!$D$8)="P0"),OR(CELL("format",'S3-3 Arena'!$D$9)="P0")),FALSE),"✔ CLEAR","· not yet · press F9")</f>
@@ -8195,7 +8225,7 @@
         <v>209</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="21" cm="1" t="str">
@@ -8374,7 +8404,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8387,24 +8417,24 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="27" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8412,13 +8442,13 @@
         <v>3.14159</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D6" s="5">
         <v>0.1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8426,13 +8456,13 @@
         <v>2.71828</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D7" s="5">
         <v>0.2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8440,13 +8470,13 @@
         <v>1.41421</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D8" s="5">
         <v>0.3</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8454,13 +8484,13 @@
         <v>1.73205</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D9" s="5">
         <v>0.4</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -8491,7 +8521,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8502,7 +8532,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -8521,7 +8551,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -8532,19 +8562,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C6" s="29"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C8" s="30" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -8553,7 +8583,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C9" s="30">
         <v>8</v>
@@ -8561,7 +8591,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('S3-1 Number Skins'!$G$16:$G$50)&gt;=280*0.5,SUM('S3-2 Text Style'!$G$14:$G$39)&gt;=190*0.5,SUM('S3-3 Format Power'!$G$17:$G$51)&gt;=280*0.5),"OPEN","LOCKED")</f>
@@ -8574,7 +8604,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -8608,7 +8638,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B14" s="31" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which keys open the Format Cells dialog?  (from S3-3 Format Power)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8631,7 +8661,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B15" s="31" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which keys add an outline border?  (from S3-3 Format Power)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8654,7 +8684,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B16" s="31" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which keys remove the outline border?  (from S3-3 Format Power)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8700,7 +8730,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B18" s="31" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which KeyTips center the selected cells?  (from S3-3 Format Power)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8723,7 +8753,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B19" s="31" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which KeyTips open the Fill Color menu?  (from S3-3 Format Power)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8746,7 +8776,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B20" s="31" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which key repeats your last action?  (from S3-3 Format Power)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8769,7 +8799,7 @@
     </row>
     <row r="21" spans="1:7" ht="51.25" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B21" s="31" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","While typing a function name, which key inserts the highlighted AutoComplete suggestion?  (from F1-5 X-Ray)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -8792,7 +8822,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -8803,7 +8833,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -8831,14 +8861,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B26" s="31" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","In the Boss Arena make B6:B8 currency (Ctrl+Shift+$). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$B$6)="C2",CELL("format",'Boss Arena'!$B$6)="C2-"),OR(CELL("format",'Boss Arena'!$B$7)="C2",CELL("format",'Boss Arena'!$B$7)="C2-"),OR(CELL("format",'Boss Arena'!$B$8)="C2",CELL("format",'Boss Arena'!$B$8)="C2-")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8856,14 +8886,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B27" s="31" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","Make C6:C8 percent (Ctrl+Shift+%). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$C$6)="P0"),OR(CELL("format",'Boss Arena'!$C$7)="P0"),OR(CELL("format",'Boss Arena'!$C$8)="P0")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8881,14 +8911,14 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B28" s="31" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","Make D6:D8 dates (Ctrl+Shift+#). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D28" s="21" cm="1" t="str">
         <f t="array" ref="D28">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$D$6)="D1",CELL("format",'Boss Arena'!$D$6)="D4"),OR(CELL("format",'Boss Arena'!$D$7)="D1",CELL("format",'Boss Arena'!$D$7)="D4"),OR(CELL("format",'Boss Arena'!$D$8)="D1",CELL("format",'Boss Arena'!$D$8)="D4")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8906,14 +8936,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B29" s="31" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","Make E6:E8 times (Ctrl+Shift+@). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$E$6)="D7",CELL("format",'Boss Arena'!$E$6)="D6",CELL("format",'Boss Arena'!$E$6)="D9",CELL("format",'Boss Arena'!$E$6)="D8"),OR(CELL("format",'Boss Arena'!$E$7)="D7",CELL("format",'Boss Arena'!$E$7)="D6",CELL("format",'Boss Arena'!$E$7)="D9",CELL("format",'Boss Arena'!$E$7)="D8"),OR(CELL("format",'Boss Arena'!$E$8)="D7",CELL("format",'Boss Arena'!$E$8)="D6",CELL("format",'Boss Arena'!$E$8)="D9",CELL("format",'Boss Arena'!$E$8)="D8")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8931,14 +8961,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B30" s="31" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","F6:F8 wear currency. Reset them to General (Ctrl+Shift+~). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$F$6)="G"),OR(CELL("format",'Boss Arena'!$F$7)="G"),OR(CELL("format",'Boss Arena'!$F$8)="G")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8956,14 +8986,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B31" s="31" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","Give G6:G8 exactly 1 decimal place through Ctrl+1. Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$G$6)="F1",CELL("format",'Boss Arena'!$G$6)=",1"),OR(CELL("format",'Boss Arena'!$G$7)="F1",CELL("format",'Boss Arena'!$G$7)=",1"),OR(CELL("format",'Boss Arena'!$G$8)="F1",CELL("format",'Boss Arena'!$G$8)=",1")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -8981,14 +9011,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B32" s="31" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","Center H6:H8 with Alt, H, A, C. Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(IFERROR(AND(CELL("prefix",'Boss Arena'!$H$6)="^",CELL("prefix",'Boss Arena'!$H$7)="^",CELL("prefix",'Boss Arena'!$H$8)="^"),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -9006,14 +9036,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B33" s="31" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","Make I6 a percent with Ctrl+Shift+%, then use F4 on I7 and I8. Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(IFERROR(AND(OR(CELL("format",'Boss Arena'!$I$6)="P0"),OR(CELL("format",'Boss Arena'!$I$7)="P0"),OR(CELL("format",'Boss Arena'!$I$8)="P0")),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -9129,7 +9159,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -9142,36 +9172,36 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="27" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -9194,7 +9224,7 @@
         <v>2.345</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="I6" s="5">
         <v>0.05</v>
@@ -9220,7 +9250,7 @@
         <v>9.875999999999999</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="I7" s="5">
         <v>0.12</v>
@@ -9246,7 +9276,7 @@
         <v>4.4444</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="I8" s="5">
         <v>0.3</v>
